--- a/numerical-workflows/v2/framework/06_最终配置/房车/DeviceLvUp.xlsx
+++ b/numerical-workflows/v2/framework/06_最终配置/房车/DeviceLvUp.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DeviceLvUp" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="@Desc" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="中文说明" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DeviceLvUp" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Desc" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中文说明" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DeviceLvUp'!$B$4:$I$54</definedName>
@@ -1334,7 +1334,7 @@
         <v>20.8</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="G5" s="6" t="n"/>
       <c r="H5" s="6" t="n"/>
@@ -1355,7 +1355,7 @@
         <v>27.1</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G6" s="6" t="n"/>
       <c r="H6" s="6" t="inlineStr">
@@ -1380,7 +1380,7 @@
         <v>35.4</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G7" s="6" t="n"/>
       <c r="H7" s="6" t="inlineStr">
@@ -1405,7 +1405,7 @@
         <v>45.8</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G8" s="6" t="n"/>
       <c r="H8" s="6" t="inlineStr">
@@ -1430,7 +1430,7 @@
         <v>58.3</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G9" s="6" t="n"/>
       <c r="H9" s="6" t="inlineStr">
@@ -1455,7 +1455,7 @@
         <v>72.90000000000001</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G10" s="6" t="n"/>
       <c r="H10" s="6" t="inlineStr">
@@ -1480,7 +1480,7 @@
         <v>87.5</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G11" s="6" t="n"/>
       <c r="H11" s="6" t="inlineStr">
@@ -1505,7 +1505,7 @@
         <v>102.1</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G12" s="6" t="n"/>
       <c r="H12" s="6" t="inlineStr">
@@ -1555,7 +1555,7 @@
         <v>125</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G14" s="6" t="n"/>
       <c r="H14" s="6" t="inlineStr">
@@ -1577,10 +1577,10 @@
         <v>1</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="G15" s="6" t="n"/>
       <c r="H15" s="6" t="n"/>
@@ -1598,10 +1598,10 @@
         <v>2</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G16" s="6" t="n"/>
       <c r="H16" s="6" t="inlineStr">
@@ -1623,10 +1623,10 @@
         <v>3</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G17" s="6" t="n"/>
       <c r="H17" s="6" t="inlineStr">
@@ -1648,10 +1648,10 @@
         <v>4</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G18" s="6" t="n"/>
       <c r="H18" s="6" t="inlineStr">
@@ -1673,10 +1673,10 @@
         <v>5</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="6" t="inlineStr">
@@ -1698,10 +1698,10 @@
         <v>6</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G20" s="6" t="n"/>
       <c r="H20" s="6" t="inlineStr">
@@ -1723,10 +1723,10 @@
         <v>7</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G21" s="6" t="n"/>
       <c r="H21" s="6" t="inlineStr">
@@ -1748,10 +1748,10 @@
         <v>8</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G22" s="6" t="n"/>
       <c r="H22" s="6" t="inlineStr">
@@ -1773,7 +1773,7 @@
         <v>9</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>24</v>
@@ -1798,10 +1798,10 @@
         <v>10</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G24" s="6" t="n"/>
       <c r="H24" s="6" t="inlineStr">
@@ -1826,7 +1826,7 @@
         <v>0.5</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="G25" s="6" t="n"/>
       <c r="H25" s="6" t="n"/>
@@ -1847,7 +1847,7 @@
         <v>0.6</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G26" s="6" t="n"/>
       <c r="H26" s="6" t="inlineStr">
@@ -1872,7 +1872,7 @@
         <v>0.7</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G27" s="6" t="n"/>
       <c r="H27" s="6" t="inlineStr">
@@ -1897,7 +1897,7 @@
         <v>0.8</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G28" s="6" t="n"/>
       <c r="H28" s="6" t="inlineStr">
@@ -1922,7 +1922,7 @@
         <v>0.9</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G29" s="6" t="n"/>
       <c r="H29" s="6" t="inlineStr">
@@ -1947,7 +1947,7 @@
         <v>1</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G30" s="6" t="n"/>
       <c r="H30" s="6" t="inlineStr">
@@ -1972,7 +1972,7 @@
         <v>1.1</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G31" s="6" t="n"/>
       <c r="H31" s="6" t="inlineStr">
@@ -1997,7 +1997,7 @@
         <v>1.2</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G32" s="6" t="n"/>
       <c r="H32" s="6" t="inlineStr">
@@ -2044,10 +2044,10 @@
         <v>10</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G34" s="6" t="n"/>
       <c r="H34" s="6" t="inlineStr">
@@ -2069,10 +2069,10 @@
         <v>1</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="G35" s="6" t="n"/>
       <c r="H35" s="6" t="n"/>
@@ -2090,10 +2090,10 @@
         <v>2</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G36" s="6" t="n"/>
       <c r="H36" s="6" t="inlineStr">
@@ -2115,10 +2115,10 @@
         <v>3</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G37" s="6" t="n"/>
       <c r="H37" s="6" t="inlineStr">
@@ -2140,10 +2140,10 @@
         <v>4</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G38" s="6" t="n"/>
       <c r="H38" s="6" t="inlineStr">
@@ -2165,10 +2165,10 @@
         <v>5</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G39" s="6" t="n"/>
       <c r="H39" s="6" t="inlineStr">
@@ -2190,10 +2190,10 @@
         <v>6</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G40" s="6" t="n"/>
       <c r="H40" s="6" t="inlineStr">
@@ -2215,10 +2215,10 @@
         <v>7</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G41" s="6" t="n"/>
       <c r="H41" s="6" t="inlineStr">
@@ -2240,10 +2240,10 @@
         <v>8</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G42" s="6" t="n"/>
       <c r="H42" s="6" t="inlineStr">
@@ -2265,7 +2265,7 @@
         <v>9</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>24</v>
@@ -2293,7 +2293,7 @@
         <v>3.3</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G44" s="6" t="n"/>
       <c r="H44" s="6" t="inlineStr">
@@ -2318,7 +2318,7 @@
         <v>1250</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="G45" s="6" t="n"/>
       <c r="H45" s="6" t="n"/>
@@ -2339,7 +2339,7 @@
         <v>1500</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>1750</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G47" s="6" t="n"/>
       <c r="H47" s="6" t="inlineStr">
@@ -2393,7 +2393,7 @@
         <v>2041.7</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>2375</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>2750</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G50" s="6" t="n"/>
       <c r="H50" s="6" t="inlineStr">
@@ -2476,7 +2476,7 @@
         <v>3166.7</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>3541.7</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>4166.7</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
@@ -2961,7 +2961,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
